--- a/entity_plans/2 HUMAN RESOURCE MANAGEMENT PROFESSIONAL EXAMINATION BOARD.xlsx
+++ b/entity_plans/2 HUMAN RESOURCE MANAGEMENT PROFESSIONAL EXAMINATION BOARD.xlsx
@@ -8,6 +8,18 @@
   </bookViews>
   <sheets>
     <sheet name="Procurement Plan" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="3" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="8" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="9" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="12" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="13" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="16" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="18" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="23" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="24" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="25" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,7 +28,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="&quot;KES&quot; #,##0.00"/>
+  </numFmts>
   <fonts count="4">
     <font>
       <name val="Calibri"/>
@@ -97,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -122,6 +136,12 @@
     </xf>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -494,11 +514,11 @@
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="86" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -569,22 +589,22 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>RFQ, WOMEN, YOUTH, PWD</t>
+          <t>RFQ/RFQ WOMEN/RFQ YOUTH/RFQ PWD</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>RFQ, WOMEN, PWD</t>
+          <t>RFQ/RFQ WOMEN/RFQ PWD</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>RFQ, WOMEN, PWD</t>
+          <t>RFQ/RFQ WOMEN/RFQ PWD</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>RFQ, WOMEN, PWD</t>
+          <t>RFQ/RFQ WOMEN/RFQ PWD</t>
         </is>
       </c>
     </row>
@@ -607,22 +627,22 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>WOMEN, YOUTH</t>
+          <t>RFQ WOMEN/RFQ YOUTH</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>WOMEN</t>
+          <t>RFQ WOMEN</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>WOMEN, PWD</t>
+          <t>RFQ WOMEN/RFQ PWD</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>WOMEN, PWD</t>
+          <t>RFQ WOMEN/RFQ PWD</t>
         </is>
       </c>
     </row>
@@ -655,7 +675,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>YOUTH</t>
+          <t>RFQ YOUTH</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -683,22 +703,22 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>YOUTH, PWD</t>
+          <t>RFQ YOUTH/RFQ PWD</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>YOUTH, PWD</t>
+          <t>RFQ YOUTH/RFQ PWD</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>YOUTH, PWD</t>
+          <t>RFQ YOUTH/RFQ PWD</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>PWD</t>
+          <t>RFQ PWD</t>
         </is>
       </c>
     </row>
@@ -721,22 +741,22 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>YOUTH, PWD</t>
+          <t>RFQ YOUTH/RFQ PWD</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>YOUTH</t>
+          <t>RFQ YOUTH</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>YOUTH, PWD</t>
+          <t>RFQ YOUTH/RFQ PWD</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>YOUTH</t>
+          <t>RFQ YOUTH</t>
         </is>
       </c>
     </row>
@@ -759,7 +779,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>YOUTH, PWD</t>
+          <t>RFQ YOUTH/RFQ PWD</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -797,7 +817,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>YOUTH, PWD</t>
+          <t>RFQ YOUTH/RFQ PWD</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -835,7 +855,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>RFQ, PWD</t>
+          <t>RFQ/RFQ PWD</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -873,17 +893,17 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>WOMEN, YOUTH, PWD</t>
+          <t>RFQ WOMEN/RFQ YOUTH/RFQ PWD</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>YOUTH, PWD</t>
+          <t>RFQ YOUTH/RFQ PWD</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>YOUTH, PWD</t>
+          <t>RFQ YOUTH/RFQ PWD</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -911,7 +931,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>YOUTH</t>
+          <t>RFQ YOUTH</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -949,7 +969,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>YOUTH</t>
+          <t>RFQ YOUTH</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -987,22 +1007,22 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>WOMEN, YOUTH</t>
+          <t>RFQ WOMEN/RFQ YOUTH</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>WOMEN</t>
+          <t>RFQ WOMEN</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>WOMEN</t>
+          <t>RFQ WOMEN</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>WOMEN</t>
+          <t>RFQ WOMEN</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1045,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>WOMEN, YOUTH, PWD</t>
+          <t>RFQ WOMEN/RFQ YOUTH/RFQ PWD</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -1063,7 +1083,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>WOMEN, YOUTH, PWD</t>
+          <t>RFQ WOMEN/RFQ YOUTH/RFQ PWD</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -1078,7 +1098,7 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>WOMEN, YOUTH, PWD</t>
+          <t>RFQ WOMEN/RFQ YOUTH/RFQ PWD</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1121,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>YOUTH</t>
+          <t>RFQ YOUTH</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -1139,12 +1159,12 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>YOUTH, PWD</t>
+          <t>RFQ YOUTH/RFQ PWD</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>PWD</t>
+          <t>RFQ PWD</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -1215,7 +1235,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>YOUTH</t>
+          <t>RFQ YOUTH</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -1253,22 +1273,22 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>YOUTH</t>
+          <t>RFQ YOUTH</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>YOUTH</t>
+          <t>RFQ YOUTH</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>YOUTH</t>
+          <t>RFQ YOUTH</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>YOUTH</t>
+          <t>RFQ YOUTH</t>
         </is>
       </c>
     </row>
@@ -1291,22 +1311,22 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>PWD</t>
+          <t>RFQ PWD</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>YOUTH, PWD</t>
+          <t>RFQ YOUTH/RFQ PWD</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>PWD</t>
+          <t>RFQ PWD</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>YOUTH, PWD</t>
+          <t>RFQ YOUTH/RFQ PWD</t>
         </is>
       </c>
     </row>
@@ -1329,7 +1349,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>YOUTH</t>
+          <t>RFQ YOUTH</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -1362,7 +1382,7 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>RFQ AGPO</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -1400,7 +1420,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>OPEN, RFQ AGPO</t>
+          <t>OPEN/RFQ AGPO</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -1410,17 +1430,17 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>OPEN, PWD</t>
+          <t>OPEN/RFQ PWD</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>PWD</t>
+          <t>RFQ PWD</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>PWD</t>
+          <t>RFQ PWD</t>
         </is>
       </c>
     </row>
@@ -1519,22 +1539,22 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>PWD</t>
+          <t>RFQ PWD</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>PWD</t>
+          <t>RFQ PWD</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>PWD</t>
+          <t>RFQ PWD</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>PWD</t>
+          <t>RFQ PWD</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1587,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>PWD</t>
+          <t>RFQ PWD</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
@@ -1610,7 +1630,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>PWD</t>
+          <t>RFQ PWD</t>
         </is>
       </c>
     </row>
@@ -1675,4 +1695,2646 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Personal and Domestic Services — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>91101802</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Evening or bridal gown or dress rental</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>300.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>3500</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>1050000</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>RFQ YOUTH</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>91101802</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Evening or bridal gown or dress rental</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>700.00</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>550</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>385000</v>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>RFQ YOUTH</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Commercial &amp; Military &amp; Private Vehicles &amp; their Accessories &amp; Components — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>25101503</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Automobiles or cars</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr"/>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Financial &amp; Insurance Services — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>84131603</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Accidental injury insurance</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr"/>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>84131503</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Car or truck insurance</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>400000</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>400000</v>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr"/>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Financial Instruments, Products, Contracts and Agreements — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>64122102</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Group health insurance policy</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>300000</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>300000</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Open Tender</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr"/>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Travel &amp; Food &amp; Lodging &amp; Entertainment Services — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>90111501</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Hotels</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>2780000</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>2780000</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr"/>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>90101603</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Catering services</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>2034.00</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>500</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>1017000</v>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>90111601</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Conference centers</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>4500</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>900000</v>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr"/>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>90111601</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Conference centers</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>195.00</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>4500</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>877500</v>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="inlineStr"/>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>90111601</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Conference centers</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>630000</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>630000</v>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="inlineStr"/>
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>90101603</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Catering services</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>240.00</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>2500</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>600000</v>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>RFQ PWD</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>90111601</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Conference centers</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>6000</v>
+      </c>
+      <c r="H9" s="10" t="n">
+        <v>600000</v>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="inlineStr"/>
+      <c r="K9" s="9" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>90111601</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Conference centers</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>130.00</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>4500</v>
+      </c>
+      <c r="H10" s="10" t="n">
+        <v>585000</v>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="inlineStr"/>
+      <c r="K10" s="9" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>90111601</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Conference centers</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>126.00</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>4500</v>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>567000</v>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="inlineStr"/>
+      <c r="K11" s="9" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>90111601</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Conference centers</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="n">
+        <v>4500</v>
+      </c>
+      <c r="H12" s="10" t="n">
+        <v>562500</v>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="inlineStr"/>
+      <c r="K12" s="9" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>90111601</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Conference centers</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>114.00</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="n">
+        <v>4500</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>513000</v>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J13" s="9" t="inlineStr"/>
+      <c r="K13" s="9" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>90111601</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Conference centers</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="n">
+        <v>4500</v>
+      </c>
+      <c r="H14" s="10" t="n">
+        <v>495000</v>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr"/>
+      <c r="K14" s="9" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>90111601</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Conference centers</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>80.00</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="n">
+        <v>4500</v>
+      </c>
+      <c r="H15" s="10" t="n">
+        <v>360000</v>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="inlineStr"/>
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>90111601</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Conference centers</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>65.00</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="n">
+        <v>4500</v>
+      </c>
+      <c r="H16" s="10" t="n">
+        <v>292500</v>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="inlineStr"/>
+      <c r="K16" s="9" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>90111601</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Conference centers</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>65.00</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="n">
+        <v>4500</v>
+      </c>
+      <c r="H17" s="10" t="n">
+        <v>292500</v>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="inlineStr"/>
+      <c r="K17" s="9" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>90111601</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Conference centers</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>48.00</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="n">
+        <v>4500</v>
+      </c>
+      <c r="H18" s="10" t="n">
+        <v>216000</v>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="inlineStr"/>
+      <c r="K18" s="9" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Transportation &amp; Storage &amp; Mail Services — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>78111502</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Commercial airplane travel</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>38000</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>342000</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>78111502</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Commercial airplane travel</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>38000</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>304000</v>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Material Handling &amp; Conditioning &amp; Storage Machinery &amp; their Accessories &amp; Supplies — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>24141504</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Tamper proof or security seals</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>4430.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>95</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>420850</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>RFQ YOUTH</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Published Products — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>55111503</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Electronic encyclopedias</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>62500</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>250000</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr"/>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>RFQ</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Paper Materials &amp; Products — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>14111607</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Poster boards</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>3500.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>150</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>525000</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>RFQ PWD</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Food, Beverage &amp; Tobacco Products — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>50202310</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Spring or mineral water</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>300.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>750</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>225000</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>RFQ WOMEN</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Editorial &amp; Design &amp; Graphic &amp; Fine Art Services — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>82121506</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Publication printing</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Goods</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>1300.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>390000</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>RFQ YOUTH</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Information Technology Broadcasting &amp; Telecommunications — Items ≥ KES 200,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sr. No.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>UNSPSC/Item Code</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Item Description</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Type</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Unit of Issue</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Estimated Unit Cost</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cost</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Method</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Reservation Group</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>43233415</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Backup or archival software</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Non Consultancy Services</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Each (EA)</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>300000</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>300000</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>Request for Quotation</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>AGPO</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>RFQ PWD</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>